--- a/backend/wp_templates/N/N4 税金及附加.xlsx
+++ b/backend/wp_templates/N/N4 税金及附加.xlsx
@@ -22,10 +22,6 @@
     <sheet name="调整分录汇总表N4-3" sheetId="28" r:id="rId8"/>
     <sheet name="GT_Custom" sheetId="24" state="hidden" r:id="rId9"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId10"/>
-    <externalReference r:id="rId11"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'调整分录汇总表N4-3'!$A$1:$J$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'附注披露信息（国企）'!$A$1:$E$17</definedName>
@@ -3621,82 +3617,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="底稿目录"/>
-      <sheetName val="税金及附加审计程序表O2A "/>
-      <sheetName val="税金及附加审定表O2"/>
-      <sheetName val="税金及附加附注披露信息（上市公司）O2-1"/>
-      <sheetName val="税金及附加附注披露信息（国企）O2-1"/>
-      <sheetName val="税金及附加明细表O2-2"/>
-      <sheetName val="调整分录汇总表O2-3"/>
-      <sheetName val="GT_Custom"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>被审计单位：</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="底稿目录"/>
-      <sheetName val="税金及附加审计程序表O2A "/>
-      <sheetName val="税金及附加审定表O2"/>
-      <sheetName val="税金及附加附注披露信息（上市公司）O2-1"/>
-      <sheetName val="税金及附加附注披露信息（国企）O2-1"/>
-      <sheetName val="税金及附加明细表O2-2"/>
-      <sheetName val="调整分录汇总表O2-2-1"/>
-      <sheetName val="GT_Custom"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>会计期间：2023X年度</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>编制日期：</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>复核人：</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -4678,19 +4598,16 @@
     </row>
     <row r="3" spans="1:10" ht="21" customHeight="1">
       <c r="A3" s="226" t="str">
-        <f>[1]底稿目录!A2</f>
         <v>被审计单位：</v>
       </c>
       <c r="B3" s="226"/>
       <c r="C3" s="226"/>
       <c r="D3" s="88" t="e">
-        <f>[1]底稿目录!A4</f>
         <v>#REF!</v>
       </c>
       <c r="E3" s="88"/>
       <c r="F3" s="88"/>
       <c r="G3" s="89" t="str">
-        <f>[2]底稿目录!A5</f>
         <v>编制日期：</v>
       </c>
       <c r="H3" s="88"/>
@@ -4701,13 +4618,11 @@
     </row>
     <row r="4" spans="1:10" ht="23.25" customHeight="1">
       <c r="A4" s="226" t="str">
-        <f>[2]底稿目录!A3</f>
         <v>会计期间：2023X年度</v>
       </c>
       <c r="B4" s="226"/>
       <c r="C4" s="226"/>
       <c r="D4" s="88" t="str">
-        <f>[2]底稿目录!A6</f>
         <v>复核人：</v>
       </c>
       <c r="E4" s="88"/>

--- a/backend/wp_templates/N/N4 税金及附加.xlsx
+++ b/backend/wp_templates/N/N4 税金及附加.xlsx
@@ -7116,7 +7116,7 @@
       <c r="C9" s="24"/>
       <c r="D9" s="24"/>
       <c r="E9" s="25">
-        <f>B9+C9+N4</f>
+        <f>B9+C9+D9</f>
         <v>0</v>
       </c>
       <c r="F9" s="26"/>
@@ -7357,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="29">
-        <f>SUM(D4:N18)</f>
+        <f>SUM(D9:D18)</f>
         <v>0</v>
       </c>
       <c r="E19" s="29">
